--- a/output/yearly_population_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_74_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5763</v>
+        <v>5416</v>
       </c>
       <c r="C2" t="n">
-        <v>6406</v>
+        <v>6234</v>
       </c>
       <c r="D2" t="n">
-        <v>34809</v>
+        <v>37196</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2976</v>
+        <v>3241</v>
       </c>
       <c r="C3" t="n">
-        <v>5795</v>
+        <v>5859</v>
       </c>
       <c r="D3" t="n">
-        <v>15876</v>
+        <v>16343</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2665</v>
+        <v>2671</v>
       </c>
       <c r="C4" t="n">
-        <v>6685</v>
+        <v>4668</v>
       </c>
       <c r="D4" t="n">
-        <v>7141</v>
+        <v>8787</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1799</v>
+        <v>1734</v>
       </c>
       <c r="C5" t="n">
-        <v>5468</v>
+        <v>3693</v>
       </c>
       <c r="D5" t="n">
-        <v>2523</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>971</v>
+        <v>1018</v>
       </c>
       <c r="C6" t="n">
-        <v>3423</v>
+        <v>2611</v>
       </c>
       <c r="D6" t="n">
-        <v>1066</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>447</v>
+        <v>497</v>
       </c>
       <c r="C7" t="n">
-        <v>1691</v>
+        <v>1752</v>
       </c>
       <c r="D7" t="n">
-        <v>645</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>669</v>
+        <v>923</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>411</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>28</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6582</v>
+        <v>6937</v>
       </c>
       <c r="C2" t="n">
-        <v>8398</v>
+        <v>8088</v>
       </c>
       <c r="D2" t="n">
-        <v>31234</v>
+        <v>30916</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3386</v>
+        <v>3405</v>
       </c>
       <c r="C3" t="n">
-        <v>5399</v>
+        <v>5312</v>
       </c>
       <c r="D3" t="n">
-        <v>17384</v>
+        <v>18080</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2401</v>
+        <v>2497</v>
       </c>
       <c r="C4" t="n">
-        <v>6063</v>
+        <v>5086</v>
       </c>
       <c r="D4" t="n">
-        <v>8349</v>
+        <v>9753</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1922</v>
+        <v>1887</v>
       </c>
       <c r="C5" t="n">
-        <v>5862</v>
+        <v>4065</v>
       </c>
       <c r="D5" t="n">
-        <v>3131</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1213</v>
+        <v>1217</v>
       </c>
       <c r="C6" t="n">
-        <v>4312</v>
+        <v>3038</v>
       </c>
       <c r="D6" t="n">
-        <v>1275</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>596</v>
+        <v>641</v>
       </c>
       <c r="C7" t="n">
-        <v>2437</v>
+        <v>2112</v>
       </c>
       <c r="D7" t="n">
-        <v>693</v>
+        <v>782</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C8" t="n">
-        <v>1109</v>
+        <v>1280</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>447</v>
+        <v>617</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
         <v>124</v>
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>28</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7791</v>
+        <v>7256</v>
       </c>
       <c r="C2" t="n">
-        <v>9735</v>
+        <v>15742</v>
       </c>
       <c r="D2" t="n">
-        <v>31164</v>
+        <v>30635</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3818</v>
+        <v>3907</v>
       </c>
       <c r="C3" t="n">
-        <v>5873</v>
+        <v>5716</v>
       </c>
       <c r="D3" t="n">
-        <v>17933</v>
+        <v>18463</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2376</v>
+        <v>2442</v>
       </c>
       <c r="C4" t="n">
-        <v>5591</v>
+        <v>5029</v>
       </c>
       <c r="D4" t="n">
-        <v>9316</v>
+        <v>10561</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1890</v>
+        <v>1920</v>
       </c>
       <c r="C5" t="n">
-        <v>5824</v>
+        <v>4372</v>
       </c>
       <c r="D5" t="n">
-        <v>3787</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1361</v>
+        <v>1352</v>
       </c>
       <c r="C6" t="n">
-        <v>4856</v>
+        <v>3434</v>
       </c>
       <c r="D6" t="n">
-        <v>1495</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>750</v>
+        <v>779</v>
       </c>
       <c r="C7" t="n">
-        <v>3165</v>
+        <v>2462</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>891</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>340</v>
+        <v>368</v>
       </c>
       <c r="C8" t="n">
-        <v>1629</v>
+        <v>1605</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C9" t="n">
-        <v>688</v>
+        <v>857</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>314</v>
+        <v>409</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>125</v>
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>28</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7086</v>
+        <v>6679</v>
       </c>
       <c r="C2" t="n">
-        <v>6697</v>
+        <v>10704</v>
       </c>
       <c r="D2" t="n">
-        <v>25791</v>
+        <v>25394</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4431</v>
+        <v>4543</v>
       </c>
       <c r="C3" t="n">
-        <v>9036</v>
+        <v>9452</v>
       </c>
       <c r="D3" t="n">
-        <v>19216</v>
+        <v>20082</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1746</v>
+        <v>1774</v>
       </c>
       <c r="C4" t="n">
-        <v>8650</v>
+        <v>6948</v>
       </c>
       <c r="D4" t="n">
-        <v>8699</v>
+        <v>10281</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1257</v>
+        <v>1249</v>
       </c>
       <c r="C5" t="n">
-        <v>4758</v>
+        <v>3365</v>
       </c>
       <c r="D5" t="n">
-        <v>2483</v>
+        <v>3274</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>693</v>
+        <v>719</v>
       </c>
       <c r="C6" t="n">
-        <v>3101</v>
+        <v>2412</v>
       </c>
       <c r="D6" t="n">
-        <v>749</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>314</v>
+        <v>340</v>
       </c>
       <c r="C7" t="n">
-        <v>1596</v>
+        <v>1572</v>
       </c>
       <c r="D7" t="n">
-        <v>471</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>674</v>
+        <v>839</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>400</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
         <v>122</v>
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>27</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4241</v>
+        <v>4039</v>
       </c>
       <c r="C2" t="n">
-        <v>3873</v>
+        <v>5166</v>
       </c>
       <c r="D2" t="n">
-        <v>18333</v>
+        <v>17889</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4759</v>
+        <v>4691</v>
       </c>
       <c r="C3" t="n">
-        <v>7243</v>
+        <v>9085</v>
       </c>
       <c r="D3" t="n">
-        <v>19187</v>
+        <v>19840</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2399</v>
+        <v>2449</v>
       </c>
       <c r="C4" t="n">
-        <v>8897</v>
+        <v>8157</v>
       </c>
       <c r="D4" t="n">
-        <v>10032</v>
+        <v>11478</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="C5" t="n">
-        <v>6494</v>
+        <v>4935</v>
       </c>
       <c r="D5" t="n">
-        <v>3230</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>823</v>
+        <v>848</v>
       </c>
       <c r="C6" t="n">
-        <v>3862</v>
+        <v>2888</v>
       </c>
       <c r="D6" t="n">
-        <v>928</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="C7" t="n">
-        <v>2118</v>
+        <v>1916</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>930</v>
+        <v>1090</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>350</v>
+        <v>444</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
         <v>209</v>
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>26</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3834</v>
+        <v>4037</v>
       </c>
       <c r="C2" t="n">
-        <v>6932</v>
+        <v>6059</v>
       </c>
       <c r="D2" t="n">
-        <v>14414</v>
+        <v>19003</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3817</v>
+        <v>3715</v>
       </c>
       <c r="C3" t="n">
-        <v>4987</v>
+        <v>6422</v>
       </c>
       <c r="D3" t="n">
-        <v>17781</v>
+        <v>18241</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2929</v>
+        <v>2911</v>
       </c>
       <c r="C4" t="n">
-        <v>7902</v>
+        <v>8441</v>
       </c>
       <c r="D4" t="n">
-        <v>11221</v>
+        <v>12493</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1606</v>
+        <v>1630</v>
       </c>
       <c r="C5" t="n">
-        <v>7551</v>
+        <v>6395</v>
       </c>
       <c r="D5" t="n">
-        <v>4176</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>964</v>
+        <v>992</v>
       </c>
       <c r="C6" t="n">
-        <v>4987</v>
+        <v>3764</v>
       </c>
       <c r="D6" t="n">
-        <v>1247</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="C7" t="n">
-        <v>2889</v>
+        <v>2353</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -2419,10 +2419,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>1416</v>
+        <v>1432</v>
       </c>
       <c r="D8" t="n">
         <v>360</v>
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>569</v>
+        <v>688</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" t="n">
         <v>36</v>
-      </c>
-      <c r="D16" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2313</v>
+        <v>2403</v>
       </c>
       <c r="C2" t="n">
-        <v>3233</v>
+        <v>2848</v>
       </c>
       <c r="D2" t="n">
-        <v>10077</v>
+        <v>13264</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3688</v>
+        <v>3690</v>
       </c>
       <c r="C3" t="n">
-        <v>5488</v>
+        <v>6104</v>
       </c>
       <c r="D3" t="n">
-        <v>17032</v>
+        <v>17911</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3229</v>
+        <v>3192</v>
       </c>
       <c r="C4" t="n">
-        <v>7620</v>
+        <v>8416</v>
       </c>
       <c r="D4" t="n">
-        <v>12025</v>
+        <v>13258</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1671</v>
+        <v>1718</v>
       </c>
       <c r="C5" t="n">
-        <v>8772</v>
+        <v>7836</v>
       </c>
       <c r="D5" t="n">
-        <v>4426</v>
+        <v>5388</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>798</v>
+        <v>829</v>
       </c>
       <c r="C6" t="n">
-        <v>5890</v>
+        <v>4512</v>
       </c>
       <c r="D6" t="n">
-        <v>1225</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C7" t="n">
-        <v>2854</v>
+        <v>2536</v>
       </c>
       <c r="D7" t="n">
-        <v>569</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>987</v>
+        <v>1109</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
         <v>284</v>
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n">
         <v>35</v>
-      </c>
-      <c r="D15" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>23</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2541</v>
+        <v>2711</v>
       </c>
       <c r="C2" t="n">
-        <v>4271</v>
+        <v>5605</v>
       </c>
       <c r="D2" t="n">
-        <v>11036</v>
+        <v>17833</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2675</v>
+        <v>2705</v>
       </c>
       <c r="C3" t="n">
-        <v>3980</v>
+        <v>4127</v>
       </c>
       <c r="D3" t="n">
-        <v>15105</v>
+        <v>16247</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3013</v>
+        <v>2993</v>
       </c>
       <c r="C4" t="n">
-        <v>6531</v>
+        <v>7234</v>
       </c>
       <c r="D4" t="n">
-        <v>12428</v>
+        <v>13569</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2028</v>
+        <v>2047</v>
       </c>
       <c r="C5" t="n">
-        <v>8165</v>
+        <v>7929</v>
       </c>
       <c r="D5" t="n">
-        <v>5385</v>
+        <v>6357</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1016</v>
+        <v>1051</v>
       </c>
       <c r="C6" t="n">
-        <v>7084</v>
+        <v>5962</v>
       </c>
       <c r="D6" t="n">
-        <v>1639</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>4098</v>
+        <v>3334</v>
       </c>
       <c r="D7" t="n">
-        <v>652</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1664</v>
+        <v>1647</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>496</v>
+        <v>571</v>
       </c>
       <c r="D9" t="n">
         <v>292</v>
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="C2" t="n">
-        <v>2752</v>
+        <v>3116</v>
       </c>
       <c r="D2" t="n">
-        <v>8920</v>
+        <v>13082</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2306</v>
+        <v>2372</v>
       </c>
       <c r="C3" t="n">
-        <v>3719</v>
+        <v>4270</v>
       </c>
       <c r="D3" t="n">
-        <v>13940</v>
+        <v>15553</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2686</v>
+        <v>2680</v>
       </c>
       <c r="C4" t="n">
-        <v>5554</v>
+        <v>6039</v>
       </c>
       <c r="D4" t="n">
-        <v>12503</v>
+        <v>13776</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2213</v>
+        <v>2206</v>
       </c>
       <c r="C5" t="n">
-        <v>7728</v>
+        <v>7745</v>
       </c>
       <c r="D5" t="n">
-        <v>6016</v>
+        <v>6986</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1185</v>
+        <v>1240</v>
       </c>
       <c r="C6" t="n">
-        <v>7706</v>
+        <v>6876</v>
       </c>
       <c r="D6" t="n">
-        <v>1991</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="C7" t="n">
-        <v>5079</v>
+        <v>4146</v>
       </c>
       <c r="D7" t="n">
-        <v>724</v>
+        <v>805</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>2192</v>
+        <v>2100</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>571</v>
+        <v>644</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3400,7 +3400,7 @@
         <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3414,7 +3414,7 @@
         <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2960</v>
+        <v>3252</v>
       </c>
       <c r="C2" t="n">
-        <v>12450</v>
+        <v>13385</v>
       </c>
       <c r="D2" t="n">
-        <v>11498</v>
+        <v>10969</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1826</v>
+        <v>1863</v>
       </c>
       <c r="C3" t="n">
-        <v>2968</v>
+        <v>3392</v>
       </c>
       <c r="D3" t="n">
-        <v>12445</v>
+        <v>14261</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2220</v>
+        <v>2237</v>
       </c>
       <c r="C4" t="n">
-        <v>4663</v>
+        <v>5166</v>
       </c>
       <c r="D4" t="n">
-        <v>12329</v>
+        <v>13613</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2166</v>
+        <v>2159</v>
       </c>
       <c r="C5" t="n">
-        <v>6690</v>
+        <v>6896</v>
       </c>
       <c r="D5" t="n">
-        <v>6704</v>
+        <v>7686</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1422</v>
+        <v>1456</v>
       </c>
       <c r="C6" t="n">
-        <v>7649</v>
+        <v>7151</v>
       </c>
       <c r="D6" t="n">
-        <v>2467</v>
+        <v>2944</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="C7" t="n">
-        <v>6105</v>
+        <v>5201</v>
       </c>
       <c r="D7" t="n">
-        <v>865</v>
+        <v>984</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>3181</v>
+        <v>2800</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1100</v>
+        <v>1120</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>37</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4931</v>
+        <v>6004</v>
       </c>
       <c r="C2" t="n">
-        <v>3415</v>
+        <v>9551</v>
       </c>
       <c r="D2" t="n">
-        <v>6690</v>
+        <v>19628</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2141</v>
+        <v>2352</v>
       </c>
       <c r="C2" t="n">
-        <v>7171</v>
+        <v>7709</v>
       </c>
       <c r="D2" t="n">
-        <v>8554</v>
+        <v>8074</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2511</v>
+        <v>2571</v>
       </c>
       <c r="C3" t="n">
-        <v>5353</v>
+        <v>5928</v>
       </c>
       <c r="D3" t="n">
-        <v>13419</v>
+        <v>15307</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3134</v>
+        <v>3136</v>
       </c>
       <c r="C4" t="n">
-        <v>6880</v>
+        <v>7469</v>
       </c>
       <c r="D4" t="n">
-        <v>12616</v>
+        <v>13998</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1353</v>
+        <v>1385</v>
       </c>
       <c r="C5" t="n">
-        <v>10374</v>
+        <v>10041</v>
       </c>
       <c r="D5" t="n">
-        <v>6035</v>
+        <v>6976</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="C6" t="n">
-        <v>7407</v>
+        <v>6498</v>
       </c>
       <c r="D6" t="n">
-        <v>1946</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>3117</v>
+        <v>2744</v>
       </c>
       <c r="D7" t="n">
-        <v>542</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1078</v>
+        <v>1097</v>
       </c>
       <c r="D8" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
         <v>36</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6475</v>
+        <v>7206</v>
       </c>
       <c r="C2" t="n">
-        <v>5920</v>
+        <v>5229</v>
       </c>
       <c r="D2" t="n">
-        <v>12207</v>
+        <v>23459</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2096</v>
+        <v>2551</v>
       </c>
       <c r="C3" t="n">
-        <v>1748</v>
+        <v>4813</v>
       </c>
       <c r="D3" t="n">
-        <v>1816</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3939</v>
+        <v>4823</v>
       </c>
       <c r="C2" t="n">
-        <v>6570</v>
+        <v>3631</v>
       </c>
       <c r="D2" t="n">
-        <v>17633</v>
+        <v>25013</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3568</v>
+        <v>4005</v>
       </c>
       <c r="C3" t="n">
-        <v>3573</v>
+        <v>4353</v>
       </c>
       <c r="D3" t="n">
-        <v>3428</v>
+        <v>6926</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>944</v>
+        <v>1142</v>
       </c>
       <c r="C4" t="n">
-        <v>1084</v>
+        <v>2864</v>
       </c>
       <c r="D4" t="n">
-        <v>1547</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
         <v>166</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4865</v>
+        <v>4919</v>
       </c>
       <c r="C2" t="n">
-        <v>11788</v>
+        <v>5839</v>
       </c>
       <c r="D2" t="n">
-        <v>19783</v>
+        <v>35247</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3095</v>
+        <v>3630</v>
       </c>
       <c r="C3" t="n">
-        <v>4559</v>
+        <v>3439</v>
       </c>
       <c r="D3" t="n">
-        <v>5453</v>
+        <v>9321</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1938</v>
+        <v>2187</v>
       </c>
       <c r="C4" t="n">
-        <v>2460</v>
+        <v>3606</v>
       </c>
       <c r="D4" t="n">
-        <v>1846</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>448</v>
+        <v>519</v>
       </c>
       <c r="C5" t="n">
-        <v>696</v>
+        <v>1664</v>
       </c>
       <c r="D5" t="n">
-        <v>1219</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5361,10 +5361,10 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6337</v>
+        <v>5216</v>
       </c>
       <c r="C2" t="n">
-        <v>7521</v>
+        <v>5564</v>
       </c>
       <c r="D2" t="n">
-        <v>32361</v>
+        <v>30958</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3226</v>
+        <v>3480</v>
       </c>
       <c r="C3" t="n">
-        <v>7257</v>
+        <v>4054</v>
       </c>
       <c r="D3" t="n">
-        <v>7247</v>
+        <v>12605</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2130</v>
+        <v>2447</v>
       </c>
       <c r="C4" t="n">
-        <v>3557</v>
+        <v>3408</v>
       </c>
       <c r="D4" t="n">
-        <v>2430</v>
+        <v>3954</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>991</v>
+        <v>1111</v>
       </c>
       <c r="C5" t="n">
-        <v>1612</v>
+        <v>2636</v>
       </c>
       <c r="D5" t="n">
-        <v>1296</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="C6" t="n">
-        <v>496</v>
+        <v>981</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
         <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5599,10 +5599,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5633,7 +5633,7 @@
         <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6298</v>
+        <v>6110</v>
       </c>
       <c r="C2" t="n">
-        <v>11053</v>
+        <v>8081</v>
       </c>
       <c r="D2" t="n">
-        <v>31267</v>
+        <v>27410</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3459</v>
+        <v>3168</v>
       </c>
       <c r="C3" t="n">
-        <v>6053</v>
+        <v>3943</v>
       </c>
       <c r="D3" t="n">
-        <v>9928</v>
+        <v>13648</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1673</v>
+        <v>1817</v>
       </c>
       <c r="C4" t="n">
-        <v>4620</v>
+        <v>3048</v>
       </c>
       <c r="D4" t="n">
-        <v>2802</v>
+        <v>4723</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>815</v>
+        <v>920</v>
       </c>
       <c r="C5" t="n">
-        <v>1932</v>
+        <v>2213</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>709</v>
+        <v>1211</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>272</v>
+        <v>415</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>365</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4689</v>
+        <v>5195</v>
       </c>
       <c r="C2" t="n">
-        <v>8652</v>
+        <v>6028</v>
       </c>
       <c r="D2" t="n">
-        <v>32050</v>
+        <v>24117</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4055</v>
+        <v>3837</v>
       </c>
       <c r="C3" t="n">
-        <v>7751</v>
+        <v>5473</v>
       </c>
       <c r="D3" t="n">
-        <v>12937</v>
+        <v>14955</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2260</v>
+        <v>2162</v>
       </c>
       <c r="C4" t="n">
-        <v>5404</v>
+        <v>3525</v>
       </c>
       <c r="D4" t="n">
-        <v>4221</v>
+        <v>6333</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1103</v>
+        <v>1223</v>
       </c>
       <c r="C5" t="n">
-        <v>3491</v>
+        <v>2655</v>
       </c>
       <c r="D5" t="n">
-        <v>1475</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>519</v>
+        <v>577</v>
       </c>
       <c r="C6" t="n">
-        <v>1404</v>
+        <v>1763</v>
       </c>
       <c r="D6" t="n">
-        <v>819</v>
+        <v>927</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="C7" t="n">
-        <v>520</v>
+        <v>859</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>249</v>
+        <v>326</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,10 +6224,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6308,10 +6308,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3583</v>
+        <v>4184</v>
       </c>
       <c r="C2" t="n">
-        <v>6124</v>
+        <v>8450</v>
       </c>
       <c r="D2" t="n">
-        <v>27912</v>
+        <v>29617</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3600</v>
+        <v>3703</v>
       </c>
       <c r="C3" t="n">
-        <v>7134</v>
+        <v>5003</v>
       </c>
       <c r="D3" t="n">
-        <v>15063</v>
+        <v>15344</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2694</v>
+        <v>2578</v>
       </c>
       <c r="C4" t="n">
-        <v>6620</v>
+        <v>4502</v>
       </c>
       <c r="D4" t="n">
-        <v>5766</v>
+        <v>7795</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C5" t="n">
-        <v>4465</v>
+        <v>3075</v>
       </c>
       <c r="D5" t="n">
-        <v>1916</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>732</v>
+        <v>818</v>
       </c>
       <c r="C6" t="n">
-        <v>2476</v>
+        <v>2213</v>
       </c>
       <c r="D6" t="n">
-        <v>927</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="C7" t="n">
-        <v>987</v>
+        <v>1328</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>387</v>
+        <v>589</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>28</v>
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_74_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5416</v>
+        <v>8948</v>
       </c>
       <c r="C2" t="n">
-        <v>6234</v>
+        <v>8313</v>
       </c>
       <c r="D2" t="n">
-        <v>37196</v>
+        <v>16517</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3241</v>
+        <v>4381</v>
       </c>
       <c r="C3" t="n">
-        <v>5859</v>
+        <v>5693</v>
       </c>
       <c r="D3" t="n">
-        <v>16343</v>
+        <v>12522</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2671</v>
+        <v>3261</v>
       </c>
       <c r="C4" t="n">
-        <v>4668</v>
+        <v>4296</v>
       </c>
       <c r="D4" t="n">
-        <v>8787</v>
+        <v>6543</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1734</v>
+        <v>2020</v>
       </c>
       <c r="C5" t="n">
-        <v>3693</v>
+        <v>3248</v>
       </c>
       <c r="D5" t="n">
-        <v>3578</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1018</v>
+        <v>1261</v>
       </c>
       <c r="C6" t="n">
-        <v>2611</v>
+        <v>2433</v>
       </c>
       <c r="D6" t="n">
-        <v>1376</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>497</v>
+        <v>649</v>
       </c>
       <c r="C7" t="n">
-        <v>1752</v>
+        <v>1490</v>
       </c>
       <c r="D7" t="n">
-        <v>697</v>
+        <v>627</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>248</v>
       </c>
       <c r="C8" t="n">
-        <v>923</v>
+        <v>745</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C9" t="n">
-        <v>411</v>
+        <v>350</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6937</v>
+        <v>9201</v>
       </c>
       <c r="C2" t="n">
-        <v>8088</v>
+        <v>12375</v>
       </c>
       <c r="D2" t="n">
-        <v>30916</v>
+        <v>22791</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3405</v>
+        <v>5205</v>
       </c>
       <c r="C3" t="n">
-        <v>5312</v>
+        <v>6081</v>
       </c>
       <c r="D3" t="n">
-        <v>18080</v>
+        <v>12235</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2497</v>
+        <v>3216</v>
       </c>
       <c r="C4" t="n">
-        <v>5086</v>
+        <v>4904</v>
       </c>
       <c r="D4" t="n">
-        <v>9753</v>
+        <v>7377</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1887</v>
+        <v>2286</v>
       </c>
       <c r="C5" t="n">
-        <v>4065</v>
+        <v>3652</v>
       </c>
       <c r="D5" t="n">
-        <v>4234</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1217</v>
+        <v>1457</v>
       </c>
       <c r="C6" t="n">
-        <v>3038</v>
+        <v>2791</v>
       </c>
       <c r="D6" t="n">
-        <v>1695</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>641</v>
+        <v>826</v>
       </c>
       <c r="C7" t="n">
-        <v>2112</v>
+        <v>1923</v>
       </c>
       <c r="D7" t="n">
-        <v>782</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>275</v>
+        <v>374</v>
       </c>
       <c r="C8" t="n">
-        <v>1280</v>
+        <v>1065</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="C9" t="n">
-        <v>617</v>
+        <v>520</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7256</v>
+        <v>9876</v>
       </c>
       <c r="C2" t="n">
-        <v>15742</v>
+        <v>13955</v>
       </c>
       <c r="D2" t="n">
-        <v>30635</v>
+        <v>23084</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3907</v>
+        <v>5575</v>
       </c>
       <c r="C3" t="n">
-        <v>5716</v>
+        <v>7747</v>
       </c>
       <c r="D3" t="n">
-        <v>18463</v>
+        <v>12783</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2442</v>
+        <v>3428</v>
       </c>
       <c r="C4" t="n">
-        <v>5029</v>
+        <v>5285</v>
       </c>
       <c r="D4" t="n">
-        <v>10561</v>
+        <v>7828</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1920</v>
+        <v>2371</v>
       </c>
       <c r="C5" t="n">
-        <v>4372</v>
+        <v>4128</v>
       </c>
       <c r="D5" t="n">
-        <v>4900</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1352</v>
+        <v>1643</v>
       </c>
       <c r="C6" t="n">
-        <v>3434</v>
+        <v>3101</v>
       </c>
       <c r="D6" t="n">
-        <v>1997</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>779</v>
+        <v>988</v>
       </c>
       <c r="C7" t="n">
-        <v>2462</v>
+        <v>2269</v>
       </c>
       <c r="D7" t="n">
-        <v>891</v>
+        <v>760</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>368</v>
+        <v>491</v>
       </c>
       <c r="C8" t="n">
-        <v>1605</v>
+        <v>1417</v>
       </c>
       <c r="D8" t="n">
-        <v>502</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>146</v>
+        <v>196</v>
       </c>
       <c r="C9" t="n">
-        <v>857</v>
+        <v>728</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>409</v>
+        <v>363</v>
       </c>
       <c r="D10" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" t="n">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6679</v>
+        <v>9053</v>
       </c>
       <c r="C2" t="n">
-        <v>10704</v>
+        <v>9377</v>
       </c>
       <c r="D2" t="n">
-        <v>25394</v>
+        <v>18773</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4543</v>
+        <v>6530</v>
       </c>
       <c r="C3" t="n">
-        <v>9452</v>
+        <v>11303</v>
       </c>
       <c r="D3" t="n">
-        <v>20082</v>
+        <v>14295</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1774</v>
+        <v>2190</v>
       </c>
       <c r="C4" t="n">
-        <v>6948</v>
+        <v>6956</v>
       </c>
       <c r="D4" t="n">
-        <v>10281</v>
+        <v>7620</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1249</v>
+        <v>1518</v>
       </c>
       <c r="C5" t="n">
-        <v>3365</v>
+        <v>3038</v>
       </c>
       <c r="D5" t="n">
-        <v>3274</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>719</v>
+        <v>912</v>
       </c>
       <c r="C6" t="n">
-        <v>2412</v>
+        <v>2223</v>
       </c>
       <c r="D6" t="n">
-        <v>873</v>
+        <v>744</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>453</v>
       </c>
       <c r="C7" t="n">
-        <v>1572</v>
+        <v>1388</v>
       </c>
       <c r="D7" t="n">
-        <v>491</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>839</v>
+        <v>713</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="D9" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4039</v>
+        <v>5750</v>
       </c>
       <c r="C2" t="n">
-        <v>5166</v>
+        <v>3985</v>
       </c>
       <c r="D2" t="n">
-        <v>17889</v>
+        <v>13079</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4691</v>
+        <v>6585</v>
       </c>
       <c r="C3" t="n">
-        <v>9085</v>
+        <v>9401</v>
       </c>
       <c r="D3" t="n">
-        <v>19840</v>
+        <v>14230</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2449</v>
+        <v>3327</v>
       </c>
       <c r="C4" t="n">
-        <v>8157</v>
+        <v>9164</v>
       </c>
       <c r="D4" t="n">
-        <v>11478</v>
+        <v>8559</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1381</v>
+        <v>1691</v>
       </c>
       <c r="C5" t="n">
-        <v>4935</v>
+        <v>4775</v>
       </c>
       <c r="D5" t="n">
-        <v>4111</v>
+        <v>3042</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>848</v>
+        <v>1080</v>
       </c>
       <c r="C6" t="n">
-        <v>2888</v>
+        <v>2625</v>
       </c>
       <c r="D6" t="n">
-        <v>1118</v>
+        <v>917</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>321</v>
+        <v>431</v>
       </c>
       <c r="C7" t="n">
-        <v>1916</v>
+        <v>1747</v>
       </c>
       <c r="D7" t="n">
-        <v>540</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>1090</v>
+        <v>929</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>444</v>
+        <v>416</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4037</v>
+        <v>5545</v>
       </c>
       <c r="C2" t="n">
-        <v>6059</v>
+        <v>3669</v>
       </c>
       <c r="D2" t="n">
-        <v>19003</v>
+        <v>14351</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3715</v>
+        <v>5221</v>
       </c>
       <c r="C3" t="n">
-        <v>6422</v>
+        <v>6021</v>
       </c>
       <c r="D3" t="n">
-        <v>18241</v>
+        <v>13085</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2911</v>
+        <v>4113</v>
       </c>
       <c r="C4" t="n">
-        <v>8441</v>
+        <v>9091</v>
       </c>
       <c r="D4" t="n">
-        <v>12493</v>
+        <v>9278</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1630</v>
+        <v>2118</v>
       </c>
       <c r="C5" t="n">
-        <v>6395</v>
+        <v>6782</v>
       </c>
       <c r="D5" t="n">
-        <v>5117</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>992</v>
+        <v>1246</v>
       </c>
       <c r="C6" t="n">
-        <v>3764</v>
+        <v>3615</v>
       </c>
       <c r="D6" t="n">
-        <v>1534</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>461</v>
+        <v>608</v>
       </c>
       <c r="C7" t="n">
-        <v>2353</v>
+        <v>2150</v>
       </c>
       <c r="D7" t="n">
-        <v>613</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>222</v>
       </c>
       <c r="C8" t="n">
-        <v>1432</v>
+        <v>1274</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>688</v>
+        <v>615</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
         <v>24</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2403</v>
+        <v>3291</v>
       </c>
       <c r="C2" t="n">
-        <v>2848</v>
+        <v>1702</v>
       </c>
       <c r="D2" t="n">
-        <v>13264</v>
+        <v>9949</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3690</v>
+        <v>5111</v>
       </c>
       <c r="C3" t="n">
-        <v>6104</v>
+        <v>5019</v>
       </c>
       <c r="D3" t="n">
-        <v>17911</v>
+        <v>12912</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3192</v>
+        <v>4543</v>
       </c>
       <c r="C4" t="n">
-        <v>8416</v>
+        <v>8743</v>
       </c>
       <c r="D4" t="n">
-        <v>13258</v>
+        <v>9806</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1718</v>
+        <v>2218</v>
       </c>
       <c r="C5" t="n">
-        <v>7836</v>
+        <v>8203</v>
       </c>
       <c r="D5" t="n">
-        <v>5388</v>
+        <v>4184</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>829</v>
+        <v>1079</v>
       </c>
       <c r="C6" t="n">
-        <v>4512</v>
+        <v>4509</v>
       </c>
       <c r="D6" t="n">
-        <v>1488</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>205</v>
       </c>
       <c r="C7" t="n">
-        <v>2536</v>
+        <v>2302</v>
       </c>
       <c r="D7" t="n">
-        <v>605</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1109</v>
+        <v>1002</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
         <v>165</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
         <v>23</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2711</v>
+        <v>5067</v>
       </c>
       <c r="C2" t="n">
-        <v>5605</v>
+        <v>5653</v>
       </c>
       <c r="D2" t="n">
-        <v>17833</v>
+        <v>10459</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2705</v>
+        <v>3718</v>
       </c>
       <c r="C3" t="n">
-        <v>4127</v>
+        <v>3103</v>
       </c>
       <c r="D3" t="n">
-        <v>16247</v>
+        <v>11641</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2993</v>
+        <v>4180</v>
       </c>
       <c r="C4" t="n">
-        <v>7234</v>
+        <v>6773</v>
       </c>
       <c r="D4" t="n">
-        <v>13569</v>
+        <v>10014</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2047</v>
+        <v>2805</v>
       </c>
       <c r="C5" t="n">
-        <v>7929</v>
+        <v>8359</v>
       </c>
       <c r="D5" t="n">
-        <v>6357</v>
+        <v>4920</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1051</v>
+        <v>1394</v>
       </c>
       <c r="C6" t="n">
-        <v>5962</v>
+        <v>6106</v>
       </c>
       <c r="D6" t="n">
-        <v>1992</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>426</v>
       </c>
       <c r="C7" t="n">
-        <v>3334</v>
+        <v>3254</v>
       </c>
       <c r="D7" t="n">
-        <v>717</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>1647</v>
+        <v>1505</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>571</v>
+        <v>537</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1911</v>
+        <v>3608</v>
       </c>
       <c r="C2" t="n">
-        <v>3116</v>
+        <v>3292</v>
       </c>
       <c r="D2" t="n">
-        <v>13082</v>
+        <v>8901</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2372</v>
+        <v>3645</v>
       </c>
       <c r="C3" t="n">
-        <v>4270</v>
+        <v>3778</v>
       </c>
       <c r="D3" t="n">
-        <v>15553</v>
+        <v>10865</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2680</v>
+        <v>3724</v>
       </c>
       <c r="C4" t="n">
-        <v>6039</v>
+        <v>5312</v>
       </c>
       <c r="D4" t="n">
-        <v>13776</v>
+        <v>10024</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2206</v>
+        <v>3048</v>
       </c>
       <c r="C5" t="n">
-        <v>7745</v>
+        <v>7847</v>
       </c>
       <c r="D5" t="n">
-        <v>6986</v>
+        <v>5451</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1240</v>
+        <v>1665</v>
       </c>
       <c r="C6" t="n">
-        <v>6876</v>
+        <v>7076</v>
       </c>
       <c r="D6" t="n">
-        <v>2403</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>4146</v>
+        <v>4202</v>
       </c>
       <c r="D7" t="n">
-        <v>805</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>2100</v>
+        <v>1949</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3252</v>
+        <v>5244</v>
       </c>
       <c r="C2" t="n">
-        <v>13385</v>
+        <v>5445</v>
       </c>
       <c r="D2" t="n">
-        <v>10969</v>
+        <v>9347</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1863</v>
+        <v>3053</v>
       </c>
       <c r="C3" t="n">
-        <v>3392</v>
+        <v>3179</v>
       </c>
       <c r="D3" t="n">
-        <v>14261</v>
+        <v>9933</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2237</v>
+        <v>3243</v>
       </c>
       <c r="C4" t="n">
-        <v>5166</v>
+        <v>4538</v>
       </c>
       <c r="D4" t="n">
-        <v>13613</v>
+        <v>9840</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2159</v>
+        <v>2993</v>
       </c>
       <c r="C5" t="n">
-        <v>6896</v>
+        <v>6637</v>
       </c>
       <c r="D5" t="n">
-        <v>7686</v>
+        <v>5847</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1456</v>
+        <v>1993</v>
       </c>
       <c r="C6" t="n">
-        <v>7151</v>
+        <v>7318</v>
       </c>
       <c r="D6" t="n">
-        <v>2944</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>519</v>
+        <v>719</v>
       </c>
       <c r="C7" t="n">
-        <v>5201</v>
+        <v>5298</v>
       </c>
       <c r="D7" t="n">
-        <v>984</v>
+        <v>869</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="C8" t="n">
-        <v>2800</v>
+        <v>2784</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>1120</v>
+        <v>1081</v>
       </c>
       <c r="D9" t="n">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>137</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6004</v>
+        <v>8436</v>
       </c>
       <c r="C2" t="n">
-        <v>9551</v>
+        <v>5714</v>
       </c>
       <c r="D2" t="n">
-        <v>19628</v>
+        <v>5327</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2352</v>
+        <v>3713</v>
       </c>
       <c r="C2" t="n">
-        <v>7709</v>
+        <v>3092</v>
       </c>
       <c r="D2" t="n">
-        <v>8074</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2571</v>
+        <v>4126</v>
       </c>
       <c r="C3" t="n">
-        <v>5928</v>
+        <v>3979</v>
       </c>
       <c r="D3" t="n">
-        <v>15307</v>
+        <v>10795</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3136</v>
+        <v>4423</v>
       </c>
       <c r="C4" t="n">
-        <v>7469</v>
+        <v>6731</v>
       </c>
       <c r="D4" t="n">
-        <v>13998</v>
+        <v>10132</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1385</v>
+        <v>1924</v>
       </c>
       <c r="C5" t="n">
-        <v>10041</v>
+        <v>9998</v>
       </c>
       <c r="D5" t="n">
-        <v>6976</v>
+        <v>5429</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>479</v>
+        <v>664</v>
       </c>
       <c r="C6" t="n">
-        <v>6498</v>
+        <v>6698</v>
       </c>
       <c r="D6" t="n">
-        <v>2281</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>2744</v>
+        <v>2728</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1097</v>
+        <v>1059</v>
       </c>
       <c r="D8" t="n">
-        <v>294</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
         <v>134</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7206</v>
+        <v>9180</v>
       </c>
       <c r="C2" t="n">
-        <v>5229</v>
+        <v>5462</v>
       </c>
       <c r="D2" t="n">
-        <v>23459</v>
+        <v>8744</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2551</v>
+        <v>3582</v>
       </c>
       <c r="C3" t="n">
-        <v>4813</v>
+        <v>2879</v>
       </c>
       <c r="D3" t="n">
-        <v>3936</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4823</v>
+        <v>5382</v>
       </c>
       <c r="C2" t="n">
-        <v>3631</v>
+        <v>3477</v>
       </c>
       <c r="D2" t="n">
-        <v>25013</v>
+        <v>17483</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4005</v>
+        <v>5240</v>
       </c>
       <c r="C3" t="n">
-        <v>4353</v>
+        <v>3787</v>
       </c>
       <c r="D3" t="n">
-        <v>6926</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1142</v>
+        <v>1590</v>
       </c>
       <c r="C4" t="n">
-        <v>2864</v>
+        <v>1729</v>
       </c>
       <c r="D4" t="n">
-        <v>1974</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4919</v>
+        <v>5132</v>
       </c>
       <c r="C2" t="n">
-        <v>5839</v>
+        <v>6316</v>
       </c>
       <c r="D2" t="n">
-        <v>35247</v>
+        <v>25794</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3630</v>
+        <v>4386</v>
       </c>
       <c r="C3" t="n">
-        <v>3439</v>
+        <v>3131</v>
       </c>
       <c r="D3" t="n">
-        <v>9321</v>
+        <v>4818</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2187</v>
+        <v>2892</v>
       </c>
       <c r="C4" t="n">
-        <v>3606</v>
+        <v>2858</v>
       </c>
       <c r="D4" t="n">
-        <v>2864</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>519</v>
+        <v>712</v>
       </c>
       <c r="C5" t="n">
-        <v>1664</v>
+        <v>1039</v>
       </c>
       <c r="D5" t="n">
-        <v>1291</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5216</v>
+        <v>5263</v>
       </c>
       <c r="C2" t="n">
-        <v>5564</v>
+        <v>5389</v>
       </c>
       <c r="D2" t="n">
-        <v>30958</v>
+        <v>25223</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3480</v>
+        <v>3910</v>
       </c>
       <c r="C3" t="n">
-        <v>4054</v>
+        <v>4152</v>
       </c>
       <c r="D3" t="n">
-        <v>12605</v>
+        <v>7667</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2447</v>
+        <v>3111</v>
       </c>
       <c r="C4" t="n">
-        <v>3408</v>
+        <v>2917</v>
       </c>
       <c r="D4" t="n">
-        <v>3954</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1111</v>
+        <v>1477</v>
       </c>
       <c r="C5" t="n">
-        <v>2636</v>
+        <v>1977</v>
       </c>
       <c r="D5" t="n">
-        <v>1511</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>285</v>
+        <v>368</v>
       </c>
       <c r="C6" t="n">
-        <v>981</v>
+        <v>674</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
         <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6110</v>
+        <v>7076</v>
       </c>
       <c r="C2" t="n">
-        <v>8081</v>
+        <v>5114</v>
       </c>
       <c r="D2" t="n">
-        <v>27410</v>
+        <v>28950</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3168</v>
+        <v>3367</v>
       </c>
       <c r="C3" t="n">
-        <v>3943</v>
+        <v>3919</v>
       </c>
       <c r="D3" t="n">
-        <v>13648</v>
+        <v>9215</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1817</v>
+        <v>2168</v>
       </c>
       <c r="C4" t="n">
-        <v>3048</v>
+        <v>2925</v>
       </c>
       <c r="D4" t="n">
-        <v>4723</v>
+        <v>2706</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>920</v>
+        <v>1200</v>
       </c>
       <c r="C5" t="n">
-        <v>2213</v>
+        <v>1806</v>
       </c>
       <c r="D5" t="n">
-        <v>1516</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>328</v>
+        <v>439</v>
       </c>
       <c r="C6" t="n">
-        <v>1211</v>
+        <v>892</v>
       </c>
       <c r="D6" t="n">
-        <v>802</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>415</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,10 +5997,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5195</v>
+        <v>7067</v>
       </c>
       <c r="C2" t="n">
-        <v>6028</v>
+        <v>7163</v>
       </c>
       <c r="D2" t="n">
-        <v>24117</v>
+        <v>21697</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3837</v>
+        <v>4405</v>
       </c>
       <c r="C3" t="n">
-        <v>5473</v>
+        <v>3972</v>
       </c>
       <c r="D3" t="n">
-        <v>14955</v>
+        <v>11995</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2162</v>
+        <v>2407</v>
       </c>
       <c r="C4" t="n">
-        <v>3525</v>
+        <v>3474</v>
       </c>
       <c r="D4" t="n">
-        <v>6333</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1223</v>
+        <v>1514</v>
       </c>
       <c r="C5" t="n">
-        <v>2655</v>
+        <v>2434</v>
       </c>
       <c r="D5" t="n">
-        <v>2116</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>577</v>
+        <v>765</v>
       </c>
       <c r="C6" t="n">
-        <v>1763</v>
+        <v>1407</v>
       </c>
       <c r="D6" t="n">
-        <v>927</v>
+        <v>805</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>188</v>
+        <v>248</v>
       </c>
       <c r="C7" t="n">
-        <v>859</v>
+        <v>644</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>326</v>
+        <v>281</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,10 +6252,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,10 +6305,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4184</v>
+        <v>6006</v>
       </c>
       <c r="C2" t="n">
-        <v>8450</v>
+        <v>8030</v>
       </c>
       <c r="D2" t="n">
-        <v>29617</v>
+        <v>17501</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3703</v>
+        <v>4703</v>
       </c>
       <c r="C3" t="n">
-        <v>5003</v>
+        <v>4963</v>
       </c>
       <c r="D3" t="n">
-        <v>15344</v>
+        <v>12683</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2578</v>
+        <v>2942</v>
       </c>
       <c r="C4" t="n">
-        <v>4502</v>
+        <v>3688</v>
       </c>
       <c r="D4" t="n">
-        <v>7795</v>
+        <v>5373</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1475</v>
+        <v>1725</v>
       </c>
       <c r="C5" t="n">
-        <v>3075</v>
+        <v>2962</v>
       </c>
       <c r="D5" t="n">
-        <v>2800</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>818</v>
+        <v>1046</v>
       </c>
       <c r="C6" t="n">
-        <v>2213</v>
+        <v>1929</v>
       </c>
       <c r="D6" t="n">
-        <v>1130</v>
+        <v>901</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>446</v>
       </c>
       <c r="C7" t="n">
-        <v>1328</v>
+        <v>1054</v>
       </c>
       <c r="D7" t="n">
-        <v>619</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="C8" t="n">
-        <v>589</v>
+        <v>469</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_74_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_74_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8948</v>
+        <v>1403</v>
       </c>
       <c r="C2" t="n">
-        <v>8313</v>
+        <v>2067</v>
       </c>
       <c r="D2" t="n">
-        <v>16517</v>
+        <v>19666</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4381</v>
+        <v>2240</v>
       </c>
       <c r="C3" t="n">
-        <v>5693</v>
+        <v>7204</v>
       </c>
       <c r="D3" t="n">
-        <v>12522</v>
+        <v>14132</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3261</v>
+        <v>1448</v>
       </c>
       <c r="C4" t="n">
-        <v>4296</v>
+        <v>10068</v>
       </c>
       <c r="D4" t="n">
-        <v>6543</v>
+        <v>5086</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2020</v>
+        <v>770</v>
       </c>
       <c r="C5" t="n">
-        <v>3248</v>
+        <v>5402</v>
       </c>
       <c r="D5" t="n">
-        <v>2385</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1261</v>
+        <v>311</v>
       </c>
       <c r="C6" t="n">
-        <v>2433</v>
+        <v>1634</v>
       </c>
       <c r="D6" t="n">
-        <v>1052</v>
+        <v>727</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>649</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>1490</v>
+        <v>582</v>
       </c>
       <c r="D7" t="n">
-        <v>627</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>248</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>745</v>
+        <v>336</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>350</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9201</v>
+        <v>1328</v>
       </c>
       <c r="C2" t="n">
-        <v>12375</v>
+        <v>2688</v>
       </c>
       <c r="D2" t="n">
-        <v>22791</v>
+        <v>15359</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5205</v>
+        <v>1558</v>
       </c>
       <c r="C3" t="n">
-        <v>6081</v>
+        <v>3916</v>
       </c>
       <c r="D3" t="n">
-        <v>12235</v>
+        <v>13978</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3216</v>
+        <v>1581</v>
       </c>
       <c r="C4" t="n">
-        <v>4904</v>
+        <v>8388</v>
       </c>
       <c r="D4" t="n">
-        <v>7377</v>
+        <v>6581</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
+        <v>957</v>
+      </c>
+      <c r="C5" t="n">
+        <v>7760</v>
+      </c>
+      <c r="D5" t="n">
         <v>2286</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3652</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2991</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1457</v>
+        <v>468</v>
       </c>
       <c r="C6" t="n">
-        <v>2791</v>
+        <v>3461</v>
       </c>
       <c r="D6" t="n">
-        <v>1232</v>
+        <v>886</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>826</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>1923</v>
+        <v>1092</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>374</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>1065</v>
+        <v>453</v>
       </c>
       <c r="D8" t="n">
-        <v>455</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>520</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9876</v>
+        <v>705</v>
       </c>
       <c r="C2" t="n">
-        <v>13955</v>
+        <v>1151</v>
       </c>
       <c r="D2" t="n">
-        <v>23084</v>
+        <v>10484</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5575</v>
+        <v>1436</v>
       </c>
       <c r="C3" t="n">
-        <v>7747</v>
+        <v>3287</v>
       </c>
       <c r="D3" t="n">
-        <v>12783</v>
+        <v>13785</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3428</v>
+        <v>1740</v>
       </c>
       <c r="C4" t="n">
-        <v>5285</v>
+        <v>7301</v>
       </c>
       <c r="D4" t="n">
-        <v>7828</v>
+        <v>7477</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2371</v>
+        <v>967</v>
       </c>
       <c r="C5" t="n">
-        <v>4128</v>
+        <v>8884</v>
       </c>
       <c r="D5" t="n">
-        <v>3573</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1643</v>
+        <v>363</v>
       </c>
       <c r="C6" t="n">
-        <v>3101</v>
+        <v>4500</v>
       </c>
       <c r="D6" t="n">
-        <v>1456</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>988</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>2269</v>
+        <v>1065</v>
       </c>
       <c r="D7" t="n">
-        <v>760</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>491</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1417</v>
+        <v>463</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>196</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>728</v>
+        <v>242</v>
       </c>
       <c r="D9" t="n">
-        <v>337</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>363</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>212</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9053</v>
+        <v>815</v>
       </c>
       <c r="C2" t="n">
-        <v>9377</v>
+        <v>3629</v>
       </c>
       <c r="D2" t="n">
-        <v>18773</v>
+        <v>15802</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6530</v>
+        <v>938</v>
       </c>
       <c r="C3" t="n">
-        <v>11303</v>
+        <v>1926</v>
       </c>
       <c r="D3" t="n">
-        <v>14295</v>
+        <v>12445</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2190</v>
+        <v>1427</v>
       </c>
       <c r="C4" t="n">
-        <v>6956</v>
+        <v>5099</v>
       </c>
       <c r="D4" t="n">
-        <v>7620</v>
+        <v>8339</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1518</v>
+        <v>1164</v>
       </c>
       <c r="C5" t="n">
-        <v>3038</v>
+        <v>8079</v>
       </c>
       <c r="D5" t="n">
-        <v>2421</v>
+        <v>3307</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>912</v>
+        <v>553</v>
       </c>
       <c r="C6" t="n">
-        <v>2223</v>
+        <v>6519</v>
       </c>
       <c r="D6" t="n">
-        <v>744</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>453</v>
+        <v>154</v>
       </c>
       <c r="C7" t="n">
-        <v>1388</v>
+        <v>2600</v>
       </c>
       <c r="D7" t="n">
-        <v>467</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
         <v>713</v>
       </c>
       <c r="D8" t="n">
-        <v>330</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>355</v>
+        <v>331</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D14" t="n">
         <v>68</v>
-      </c>
-      <c r="D14" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5750</v>
+        <v>496</v>
       </c>
       <c r="C2" t="n">
-        <v>3985</v>
+        <v>2364</v>
       </c>
       <c r="D2" t="n">
-        <v>13079</v>
+        <v>12362</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6585</v>
+        <v>780</v>
       </c>
       <c r="C3" t="n">
-        <v>9401</v>
+        <v>2413</v>
       </c>
       <c r="D3" t="n">
-        <v>14230</v>
+        <v>12184</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3327</v>
+        <v>1167</v>
       </c>
       <c r="C4" t="n">
-        <v>9164</v>
+        <v>3677</v>
       </c>
       <c r="D4" t="n">
-        <v>8559</v>
+        <v>8876</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1691</v>
+        <v>1220</v>
       </c>
       <c r="C5" t="n">
-        <v>4775</v>
+        <v>6991</v>
       </c>
       <c r="D5" t="n">
-        <v>3042</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1080</v>
+        <v>679</v>
       </c>
       <c r="C6" t="n">
-        <v>2625</v>
+        <v>7405</v>
       </c>
       <c r="D6" t="n">
-        <v>917</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>431</v>
+        <v>168</v>
       </c>
       <c r="C7" t="n">
-        <v>1747</v>
+        <v>3891</v>
       </c>
       <c r="D7" t="n">
-        <v>509</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>929</v>
+        <v>1148</v>
       </c>
       <c r="D8" t="n">
-        <v>341</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5545</v>
+        <v>698</v>
       </c>
       <c r="C2" t="n">
-        <v>3669</v>
+        <v>6652</v>
       </c>
       <c r="D2" t="n">
-        <v>14351</v>
+        <v>12096</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5221</v>
+        <v>561</v>
       </c>
       <c r="C3" t="n">
-        <v>6021</v>
+        <v>2103</v>
       </c>
       <c r="D3" t="n">
-        <v>13085</v>
+        <v>11389</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4113</v>
+        <v>882</v>
       </c>
       <c r="C4" t="n">
-        <v>9091</v>
+        <v>2993</v>
       </c>
       <c r="D4" t="n">
-        <v>9278</v>
+        <v>9146</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2118</v>
+        <v>1110</v>
       </c>
       <c r="C5" t="n">
-        <v>6782</v>
+        <v>5385</v>
       </c>
       <c r="D5" t="n">
-        <v>3849</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1246</v>
+        <v>821</v>
       </c>
       <c r="C6" t="n">
-        <v>3615</v>
+        <v>7156</v>
       </c>
       <c r="D6" t="n">
-        <v>1231</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>608</v>
+        <v>310</v>
       </c>
       <c r="C7" t="n">
-        <v>2150</v>
+        <v>5408</v>
       </c>
       <c r="D7" t="n">
-        <v>563</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>222</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>1274</v>
+        <v>2234</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>615</v>
+        <v>688</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3291</v>
+        <v>469</v>
       </c>
       <c r="C2" t="n">
-        <v>1702</v>
+        <v>3513</v>
       </c>
       <c r="D2" t="n">
-        <v>9949</v>
+        <v>8710</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5111</v>
+        <v>815</v>
       </c>
       <c r="C3" t="n">
-        <v>5019</v>
+        <v>3505</v>
       </c>
       <c r="D3" t="n">
-        <v>12912</v>
+        <v>12340</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4543</v>
+        <v>1457</v>
       </c>
       <c r="C4" t="n">
-        <v>8743</v>
+        <v>4592</v>
       </c>
       <c r="D4" t="n">
-        <v>9806</v>
+        <v>9338</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2218</v>
+        <v>830</v>
       </c>
       <c r="C5" t="n">
-        <v>8203</v>
+        <v>9033</v>
       </c>
       <c r="D5" t="n">
-        <v>4184</v>
+        <v>4176</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1079</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>4509</v>
+        <v>7053</v>
       </c>
       <c r="D6" t="n">
-        <v>1206</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>205</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>2302</v>
+        <v>2189</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1002</v>
+        <v>674</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5067</v>
+        <v>308</v>
       </c>
       <c r="C2" t="n">
-        <v>5653</v>
+        <v>2716</v>
       </c>
       <c r="D2" t="n">
-        <v>10459</v>
+        <v>7232</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3718</v>
+        <v>565</v>
       </c>
       <c r="C3" t="n">
-        <v>3103</v>
+        <v>3090</v>
       </c>
       <c r="D3" t="n">
-        <v>11641</v>
+        <v>10932</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4180</v>
+        <v>971</v>
       </c>
       <c r="C4" t="n">
-        <v>6773</v>
+        <v>3829</v>
       </c>
       <c r="D4" t="n">
-        <v>10014</v>
+        <v>9173</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2805</v>
+        <v>781</v>
       </c>
       <c r="C5" t="n">
-        <v>8359</v>
+        <v>6105</v>
       </c>
       <c r="D5" t="n">
-        <v>4920</v>
+        <v>4434</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1394</v>
+        <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>6106</v>
+        <v>6576</v>
       </c>
       <c r="D6" t="n">
-        <v>1630</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>426</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>3254</v>
+        <v>3048</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1505</v>
+        <v>814</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>537</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3608</v>
+        <v>761</v>
       </c>
       <c r="C2" t="n">
-        <v>3292</v>
+        <v>7029</v>
       </c>
       <c r="D2" t="n">
-        <v>8901</v>
+        <v>14944</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3645</v>
+        <v>371</v>
       </c>
       <c r="C3" t="n">
-        <v>3778</v>
+        <v>2498</v>
       </c>
       <c r="D3" t="n">
-        <v>10865</v>
+        <v>9552</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3724</v>
+        <v>686</v>
       </c>
       <c r="C4" t="n">
-        <v>5312</v>
+        <v>3367</v>
       </c>
       <c r="D4" t="n">
-        <v>10024</v>
+        <v>9231</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3048</v>
+        <v>783</v>
       </c>
       <c r="C5" t="n">
-        <v>7847</v>
+        <v>4754</v>
       </c>
       <c r="D5" t="n">
-        <v>5451</v>
+        <v>5163</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1665</v>
+        <v>471</v>
       </c>
       <c r="C6" t="n">
-        <v>7076</v>
+        <v>6322</v>
       </c>
       <c r="D6" t="n">
-        <v>1926</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>4202</v>
+        <v>4839</v>
       </c>
       <c r="D7" t="n">
-        <v>724</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>1949</v>
+        <v>1872</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>639</v>
+        <v>510</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>176</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5244</v>
+        <v>1006</v>
       </c>
       <c r="C2" t="n">
-        <v>5445</v>
+        <v>7386</v>
       </c>
       <c r="D2" t="n">
-        <v>9347</v>
+        <v>25507</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3053</v>
+        <v>450</v>
       </c>
       <c r="C3" t="n">
-        <v>3179</v>
+        <v>4139</v>
       </c>
       <c r="D3" t="n">
-        <v>9933</v>
+        <v>9671</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3243</v>
+        <v>472</v>
       </c>
       <c r="C4" t="n">
-        <v>4538</v>
+        <v>2846</v>
       </c>
       <c r="D4" t="n">
-        <v>9840</v>
+        <v>8917</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2993</v>
+        <v>678</v>
       </c>
       <c r="C5" t="n">
-        <v>6637</v>
+        <v>3962</v>
       </c>
       <c r="D5" t="n">
-        <v>5847</v>
+        <v>5708</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1993</v>
+        <v>562</v>
       </c>
       <c r="C6" t="n">
-        <v>7318</v>
+        <v>5503</v>
       </c>
       <c r="D6" t="n">
-        <v>2374</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>719</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>5298</v>
+        <v>5534</v>
       </c>
       <c r="D7" t="n">
-        <v>869</v>
+        <v>923</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>148</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>2784</v>
+        <v>3208</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1081</v>
+        <v>1097</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>358</v>
+        <v>319</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8436</v>
+        <v>4505</v>
       </c>
       <c r="C2" t="n">
-        <v>5714</v>
+        <v>5997</v>
       </c>
       <c r="D2" t="n">
-        <v>5327</v>
+        <v>9725</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3713</v>
+        <v>1549</v>
       </c>
       <c r="C2" t="n">
-        <v>3092</v>
+        <v>10377</v>
       </c>
       <c r="D2" t="n">
-        <v>6880</v>
+        <v>24871</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4126</v>
+        <v>560</v>
       </c>
       <c r="C3" t="n">
-        <v>3979</v>
+        <v>4921</v>
       </c>
       <c r="D3" t="n">
-        <v>10795</v>
+        <v>11267</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4423</v>
+        <v>398</v>
       </c>
       <c r="C4" t="n">
-        <v>6731</v>
+        <v>3395</v>
       </c>
       <c r="D4" t="n">
-        <v>10132</v>
+        <v>8676</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1924</v>
+        <v>551</v>
       </c>
       <c r="C5" t="n">
-        <v>9998</v>
+        <v>3376</v>
       </c>
       <c r="D5" t="n">
-        <v>5429</v>
+        <v>6027</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>664</v>
+        <v>564</v>
       </c>
       <c r="C6" t="n">
-        <v>6698</v>
+        <v>4731</v>
       </c>
       <c r="D6" t="n">
-        <v>1904</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>136</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>2728</v>
+        <v>5518</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>1059</v>
+        <v>4164</v>
       </c>
       <c r="D8" t="n">
-        <v>302</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>350</v>
+        <v>1913</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
+        <v>616</v>
+      </c>
+      <c r="D10" t="n">
         <v>161</v>
-      </c>
-      <c r="D10" t="n">
-        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>94</v>
+        <v>199</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9180</v>
+        <v>5486</v>
       </c>
       <c r="C2" t="n">
-        <v>5462</v>
+        <v>8267</v>
       </c>
       <c r="D2" t="n">
-        <v>8744</v>
+        <v>13353</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3582</v>
+        <v>1489</v>
       </c>
       <c r="C3" t="n">
-        <v>2879</v>
+        <v>2368</v>
       </c>
       <c r="D3" t="n">
-        <v>1534</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5382</v>
+        <v>3466</v>
       </c>
       <c r="C2" t="n">
-        <v>3477</v>
+        <v>9466</v>
       </c>
       <c r="D2" t="n">
-        <v>17483</v>
+        <v>12597</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5240</v>
+        <v>2953</v>
       </c>
       <c r="C3" t="n">
-        <v>3787</v>
+        <v>5094</v>
       </c>
       <c r="D3" t="n">
-        <v>2632</v>
+        <v>3806</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1590</v>
+        <v>714</v>
       </c>
       <c r="C4" t="n">
-        <v>1729</v>
+        <v>1525</v>
       </c>
       <c r="D4" t="n">
-        <v>1490</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>756</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>245</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5132</v>
+        <v>2542</v>
       </c>
       <c r="C2" t="n">
-        <v>6316</v>
+        <v>6849</v>
       </c>
       <c r="D2" t="n">
-        <v>25794</v>
+        <v>19254</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4386</v>
+        <v>2649</v>
       </c>
       <c r="C3" t="n">
-        <v>3131</v>
+        <v>6580</v>
       </c>
       <c r="D3" t="n">
-        <v>4818</v>
+        <v>5002</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2892</v>
+        <v>1606</v>
       </c>
       <c r="C4" t="n">
-        <v>2858</v>
+        <v>3651</v>
       </c>
       <c r="D4" t="n">
-        <v>1663</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>712</v>
+        <v>356</v>
       </c>
       <c r="C5" t="n">
-        <v>1039</v>
+        <v>974</v>
       </c>
       <c r="D5" t="n">
-        <v>1194</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>799</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>217</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5263</v>
+        <v>1679</v>
       </c>
       <c r="C2" t="n">
-        <v>5389</v>
+        <v>13425</v>
       </c>
       <c r="D2" t="n">
-        <v>25223</v>
+        <v>19662</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3910</v>
+        <v>2145</v>
       </c>
       <c r="C3" t="n">
-        <v>4152</v>
+        <v>5814</v>
       </c>
       <c r="D3" t="n">
-        <v>7667</v>
+        <v>6922</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3111</v>
+        <v>1839</v>
       </c>
       <c r="C4" t="n">
-        <v>2917</v>
+        <v>5262</v>
       </c>
       <c r="D4" t="n">
-        <v>2187</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1477</v>
+        <v>831</v>
       </c>
       <c r="C5" t="n">
-        <v>1977</v>
+        <v>2444</v>
       </c>
       <c r="D5" t="n">
-        <v>1227</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>368</v>
+        <v>211</v>
       </c>
       <c r="C6" t="n">
-        <v>674</v>
+        <v>640</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>293</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>194</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7076</v>
+        <v>2360</v>
       </c>
       <c r="C2" t="n">
-        <v>5114</v>
+        <v>9013</v>
       </c>
       <c r="D2" t="n">
-        <v>28950</v>
+        <v>30346</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3367</v>
+        <v>1599</v>
       </c>
       <c r="C3" t="n">
-        <v>3919</v>
+        <v>8521</v>
       </c>
       <c r="D3" t="n">
-        <v>9215</v>
+        <v>8371</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2168</v>
+        <v>1705</v>
       </c>
       <c r="C4" t="n">
-        <v>2925</v>
+        <v>5454</v>
       </c>
       <c r="D4" t="n">
-        <v>2706</v>
+        <v>3149</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1200</v>
+        <v>1150</v>
       </c>
       <c r="C5" t="n">
-        <v>1806</v>
+        <v>3881</v>
       </c>
       <c r="D5" t="n">
-        <v>1106</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="C6" t="n">
-        <v>892</v>
+        <v>1550</v>
       </c>
       <c r="D6" t="n">
-        <v>756</v>
+        <v>896</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>327</v>
+        <v>466</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7067</v>
+        <v>3293</v>
       </c>
       <c r="C2" t="n">
-        <v>7163</v>
+        <v>7906</v>
       </c>
       <c r="D2" t="n">
-        <v>21697</v>
+        <v>36540</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4405</v>
+        <v>1593</v>
       </c>
       <c r="C3" t="n">
-        <v>3972</v>
+        <v>7666</v>
       </c>
       <c r="D3" t="n">
-        <v>11995</v>
+        <v>10959</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2407</v>
+        <v>1427</v>
       </c>
       <c r="C4" t="n">
-        <v>3474</v>
+        <v>6901</v>
       </c>
       <c r="D4" t="n">
-        <v>3998</v>
+        <v>3955</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1514</v>
+        <v>1251</v>
       </c>
       <c r="C5" t="n">
-        <v>2434</v>
+        <v>4533</v>
       </c>
       <c r="D5" t="n">
-        <v>1394</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>765</v>
+        <v>685</v>
       </c>
       <c r="C6" t="n">
-        <v>1407</v>
+        <v>2652</v>
       </c>
       <c r="D6" t="n">
-        <v>805</v>
+        <v>966</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C7" t="n">
-        <v>644</v>
+        <v>975</v>
       </c>
       <c r="D7" t="n">
-        <v>554</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>281</v>
+        <v>373</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6006</v>
+        <v>2892</v>
       </c>
       <c r="C2" t="n">
-        <v>8030</v>
+        <v>4870</v>
       </c>
       <c r="D2" t="n">
-        <v>17501</v>
+        <v>28565</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4703</v>
+        <v>2315</v>
       </c>
       <c r="C3" t="n">
-        <v>4963</v>
+        <v>11132</v>
       </c>
       <c r="D3" t="n">
-        <v>12683</v>
+        <v>12288</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2942</v>
+        <v>1155</v>
       </c>
       <c r="C4" t="n">
-        <v>3688</v>
+        <v>8657</v>
       </c>
       <c r="D4" t="n">
-        <v>5373</v>
+        <v>3776</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1725</v>
+        <v>632</v>
       </c>
       <c r="C5" t="n">
-        <v>2962</v>
+        <v>2598</v>
       </c>
       <c r="D5" t="n">
-        <v>1851</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1046</v>
+        <v>227</v>
       </c>
       <c r="C6" t="n">
-        <v>1929</v>
+        <v>955</v>
       </c>
       <c r="D6" t="n">
-        <v>901</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>446</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>1054</v>
+        <v>365</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>469</v>
+        <v>277</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
